--- a/data/macro/South Korea/M2.xlsx
+++ b/data/macro/South Korea/M2.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04D1B189-CE3B-4927-ABC6-290244157285}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{08BCB5FB-51DD-450F-BCB2-E76A200295D9}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{08BCB5FB-51DD-450F-BCB2-E76A200295D9}"/>
   </bookViews>
   <sheets>
     <sheet name="KOM2Y" sheetId="1" r:id="rId1"/>
@@ -65,8 +65,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="170" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="171" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -110,19 +110,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="170" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
